--- a/tools/generated/통합문서_auvito.xlsx
+++ b/tools/generated/통합문서_auvito.xlsx
@@ -5015,179 +5015,267 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>491</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>제품전략</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>프로젝트명</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>YouTube 영상 제작 자동화 파이프라인</t>
+        </is>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>492</v>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>설계서 제목과 동일</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>493</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>제품전략</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>한 줄 소개</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>주제 입력부터 YouTube 업로드까지 이어지는 한국어 faceless YouTube 콘텐츠 반자동 제작 파이프라인</t>
+        </is>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
-        <v>494</v>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>설계서 1장 한 줄 정의 기준</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>496</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>범위</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1 범위</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Stage 0 ~ Stage 6(draft.mp4 생성)까지 구현</t>
+        </is>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
-        <v>497</v>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>설계서 15장 Phase 1 범위</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>499</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>범위</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2 범위</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Stage 7(썸네일) / Stage 8(업로드)은 계약과 인터페이스만 유지하고 실제 구현은 보류</t>
+        </is>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>500</v>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>설계서 15장 Phase 2 범위</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>502</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>범위</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>비목표</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GUI / 웹 서비스 / 다중 사용자 / 실시간 협업 / CapCut 내부 포맷 호환 / Shorts / 실사 브이로그</t>
+        </is>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>503</v>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>설계서 1장 비목표</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>506</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>운영원칙</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>아티팩트 중심</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>모든 단계의 결과는 파일(MD, JSON, 미디어)로 남기고 DB는 상태 추적용으로 사용</t>
+        </is>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>507</v>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>설계서 1장 운영 원칙</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>509</v>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>운영원칙</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>승인 게이트</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>주요 체크포인트에서 사람 승인을 받아야 다음 단계로 진행하며 기본 모드는 conditional</t>
+        </is>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
-        <v>510</v>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>설계서 2장, default.yaml</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>512</v>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>운영원칙</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>재개 가능</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>단계 중단 후 재시작 가능하며 상태 판단의 authoritative source는 SQLite</t>
+        </is>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2" t="s">
-        <v>507</v>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>설계서 1장 운영 원칙</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>514</v>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>운영원칙</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>비용 통제</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>모델 호출 횟수, 토큰, 이미지/비디오 수, 프로젝트별 총 비용을 기록하고 예산 상한을 강제</t>
+        </is>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2" t="s">
-        <v>515</v>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>설계서 1장, 9장</t>
+        </is>
       </c>
     </row>
     <row r="12" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>517</v>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>기술</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>현재 코드 의존성</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Typer, Pydantic, httpx, aiosqlite, Jinja2, edge-tts, Pillow, python-dotenv, PyYAML, Rich</t>
+        </is>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
-        <v>518</v>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>pyproject.toml 기준</t>
+        </is>
       </c>
     </row>
     <row r="13" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>520</v>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>외부 의존성</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic/OpenAI/YouTube provider, Edge TTS, FFmpeg, Pillow, SQLite 기반 로컬 실행 환경 의존</t>
+        </is>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2" t="s">
-        <v>521</v>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>설계서와 현재 코드 기준</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5247,69 +5335,103 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>464</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>AM11D/Codex</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>현재 프로젝트 코드와 종합 기술 설계서를 기준으로 통합문서 초안 작성</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>전체 문서</t>
+        </is>
       </c>
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>526</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>v0.2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>AM11D/Codex</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>예시성/창작성 데이터 제거 후 프로젝트와 설계서에 있는 사실만 반영하도록 재정리</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>프로젝트개요, 기능정의, 요구사항, 일정, 리스크</t>
+        </is>
       </c>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>490</v>
-      </c>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>v0.3</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>AM11D/Codex</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Stage 6 렌더 일부 구현과 FFmpeg 임시경로 변경 사항을 현재 코드 기준으로 반영</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>기능정의, 요구사항, 이슈·리스크, 테스트케이스</t>
+        </is>
+      </c>
+      <c r="G5" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G5" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -5399,225 +5521,357 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>533</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>F-PROJ-001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>오케스트레이션</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>프로젝트 관리</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>프로젝트 생성/조회/삭제</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>project_create, project_list, project_show, project_delete 명령과 ProjectManager CRUD</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>app/cli.py, app/core/project_manager.py, app/storage/sqlite.py에 관련 코드가 존재</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>CLI 사용자</t>
+        </is>
       </c>
       <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>535</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>일부구현</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>SCR-001</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROJ-001</t>
+        </is>
       </c>
       <c r="L3" s="2"/>
-      <c r="M3" s="2" t="s">
-        <v>536</v>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>현재 코드 기준</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>533</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>F-EXEC-001</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>오케스트레이션</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>실행 제어</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Stage 실행 상태와 실행 모드 결정</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>execution_digest, skip/resume/overwrite, stage run 상태 기록</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>app/core/stage_executor.py에 결정 로직과 상태 전이 메서드가 구현되어 있음</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>CLI 사용자</t>
+        </is>
       </c>
       <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>542</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>일부구현</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>SCR-002</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>REQ-EXEC-001, REQ-COST-001</t>
+        </is>
       </c>
       <c r="L4" s="2"/>
-      <c r="M4" s="2" t="s">
-        <v>536</v>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>현재 코드 기준</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>533</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>F-GOV-001</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>거버넌스</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>승인/비용/품질</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ApprovalService / CostGuardrail / QualityGateRunner</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>승인 체크포인트, 비용 가드레일, 자동 품질 검증</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>app/core/approval_service.py, app/core/cost_guardrail.py, app/core/quality_gate.py에 관련 코드가 존재</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>CLI 사용자</t>
+        </is>
       </c>
       <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>549</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>일부구현</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>SCR-004</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>REQ-GOV-001, REQ-COST-001</t>
+        </is>
       </c>
       <c r="L5" s="2"/>
-      <c r="M5" s="2" t="s">
-        <v>536</v>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>현재 코드 기준</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>533</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>F-BENCH-001</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>벤치마킹</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>BenchmarkReport 계약과 stage/provider 인터페이스</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>BenchmarkReport 계약, ResearchProvider, benchmark stage 골격</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>app/domain/contracts.py, app/providers/research.py, app/stages/stage1_benchmark.py 기준</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>CLI 사용자</t>
+        </is>
       </c>
       <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>557</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>골격구현</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>SCR-003</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>REQ-BENCH-001</t>
+        </is>
       </c>
       <c r="L6" s="2"/>
-      <c r="M6" s="2" t="s">
-        <v>536</v>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>현재 코드 기준</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>533</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>F-SCRIPT-001</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>대본</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ScriptContract와 script 승인 게이트</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>ScriptContract 계약, NarrativeProvider의 script 메서드, script checkpoint 설계</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>app/domain/contracts.py, app/providers/narrative.py, app/stages/stage2_script.py, app/config/default.yaml 기준</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>CLI 사용자</t>
+        </is>
       </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>563</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>골격구현</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>SCR-004</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SCRIPT-001, REQ-GOV-001</t>
+        </is>
       </c>
       <c r="L7" s="2"/>
-      <c r="M7" s="2" t="s">
-        <v>536</v>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>현재 코드 기준</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>533</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>F-MEDIA-001</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>음성/스토리보드/에셋/렌더</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Narration/Storyboard/Asset/Render 계약 체인</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>NarrationContract, StoryboardContract, AssetManifestContract, RenderPlanContract와 Stage 6 렌더 코드</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>app/domain/contracts.py, app/providers/*.py, app/services/ffmpeg_service.py, app/services/pillow_service.py, app/stages/stage3_voice.py ~ stage6_render.py 기준. Stage 3~5는 골격이고 Stage 6 렌더는 일부 구현 상태</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>CLI 사용자</t>
+        </is>
       </c>
       <c r="H8" s="2"/>
-      <c r="I8" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>570</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>일부구현</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>SCR-005, SCR-006</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>REQ-VOICE-001, REQ-VISUAL-001</t>
+        </is>
       </c>
       <c r="L8" s="2"/>
-      <c r="M8" s="2" t="s">
-        <v>536</v>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>현재 코드 기준</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5710,227 +5964,355 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>572</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SCR-001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CLI</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>프로젝트</t>
+        </is>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>535</v>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>프로젝트 관리 명령</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>project slug를 생성하거나 조회/삭제할 때</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>yt project create / list / show / delete</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>F-PROJ-001</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROJ-001</t>
+        </is>
       </c>
       <c r="M3" s="2"/>
-      <c r="N3" s="2" t="s">
-        <v>577</v>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>현재 CLI 기준</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>579</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SCR-002</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CLI</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>실행</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>파이프라인</t>
+        </is>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>542</v>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>단계 실행 및 파이프라인 실행 명령</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>특정 stage 또는 pipeline run을 제어할 때</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>yt stage run / yt pipeline run</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>F-EXEC-001</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>REQ-EXEC-001, REQ-COST-001</t>
+        </is>
       </c>
       <c r="M4" s="2"/>
-      <c r="N4" s="2" t="s">
-        <v>577</v>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>현재 CLI 기준</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>584</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SCR-003</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>작업공간</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>01_benchmark</t>
+        </is>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>557</v>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>벤치마킹 산출물 검토</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>산출물</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>BenchmarkReport와 관련 산출물을 확인할 때</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>benchmark_report.json / md / keyword bank</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>F-BENCH-001</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>REQ-BENCH-001</t>
+        </is>
       </c>
       <c r="M5" s="2"/>
-      <c r="N5" s="2" t="s">
-        <v>589</v>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>설계서 워크스페이스 구조 기준</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>591</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SCR-004</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CLI</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>승인</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>596</v>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>승인 명령 및 checkpoint 처리</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>approval_id 기준 승인/거절을 수행할 때</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>yt approvals list / approve / reject</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>F-GOV-001, F-SCRIPT-001</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>REQ-GOV-001</t>
+        </is>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2" t="s">
-        <v>597</v>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>현재 CLI와 설계서 기준</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>598</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SCR-005</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>작업공간</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>03_voice</t>
+        </is>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>602</v>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>음성/자막 산출물 검토</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>산출물</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>NarrationContract와 narration/subtitles 산출물을 확인할 때</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>narration.wav / subtitles.srt / narration_contract.json</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>F-MEDIA-001</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>REQ-VOICE-001</t>
+        </is>
       </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="2" t="s">
-        <v>589</v>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>설계서 워크스페이스 구조 기준</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>605</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SCR-006</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>작업공간</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>04_storyboard</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>05_assets</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>06_render</t>
+        </is>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>609</v>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>스토리보드/에셋/렌더 산출물 검토</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>산출물</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Storyboard, AssetManifest, RenderPlan과 draft 결과를 확인할 때</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>storyboard_contract.json / asset_manifest.json / render_plan.json / draft.mp4</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>F-MEDIA-001</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>REQ-VISUAL-001</t>
+        </is>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="2" t="s">
-        <v>589</v>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>render_plan.json / draft.mp4는 현재 Stage 6 코드 기준</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6021,282 +6403,442 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>610</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROJ-001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>프로젝트 생성/조회/삭제 명령 제공</t>
+        </is>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>613</v>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>F-PROJ-001</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>SCR-001</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>현재 코드에는 project create, list, show, delete 명령과 ProjectManager CRUD가 존재한다.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>app/cli.py, app/core/project_manager.py, app/storage/sqlite.py</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>프로젝트 slug와 상태를 저장하고 동일 slug로 조회/삭제 가능</t>
+        </is>
       </c>
       <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>534</v>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>CLI 앱</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>일부구현</t>
+        </is>
       </c>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>616</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>REQ-EXEC-001</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>단계 실행 모드와 상태 전이 관리</t>
+        </is>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>619</v>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>F-EXEC-001</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>SCR-002</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>StageExecutor는 skip/resume/overwrite 판단과 stage run 상태 전이 메서드를 제공한다.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>run_id, stage_name, execution_digest, requested_mode</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>PENDING/RUNNING/SUCCEEDED/FAILED/PARTIAL/SKIPPED 상태를 저장하는 메서드 존재</t>
+        </is>
       </c>
       <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>534</v>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>파이프라인</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>일부구현</t>
+        </is>
       </c>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>621</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>REQ-GOV-001</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>승인 체크포인트와 품질/비용 가드레일 유지</t>
+        </is>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>624</v>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>F-GOV-001</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SCR-004</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>설계서와 default.yaml에는 script, storyboard, assets_over_usd, thumbnail, upload 체크포인트와 cost_guardrail 정책이 정의되어 있다.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>app/core/approval_service.py, app/core/cost_guardrail.py, app/core/quality_gate.py, app/config/default.yaml</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>approval, cost, quality 관련 코드와 설정 파일이 존재</t>
+        </is>
       </c>
       <c r="J5" s="2"/>
-      <c r="K5" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>534</v>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>파이프라인</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>일부구현</t>
+        </is>
       </c>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>625</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>REQ-BENCH-001</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>벤치마킹 단계는 BenchmarkReport 계약을 사용</t>
+        </is>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>628</v>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>F-BENCH-001</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>SCR-003</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>BenchmarkReport 계약, ResearchProvider 인터페이스, benchmark stage 파일이 현재 프로젝트에 존재한다.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>app/domain/contracts.py, app/providers/research.py, app/stages/stage1_benchmark.py</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>벤치마킹 출력 계약과 stage/provider 골격이 존재</t>
+        </is>
       </c>
       <c r="J6" s="2"/>
-      <c r="K6" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>556</v>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>파이프라인</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>골격구현</t>
+        </is>
       </c>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>630</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SCRIPT-001</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>대본 단계는 ScriptContract 계약을 사용</t>
+        </is>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>633</v>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>F-SCRIPT-001</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SCR-004</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ScriptContract 계약과 NarrativeProvider의 script 관련 인터페이스가 존재하고 script checkpoint 설계가 문서와 설정에 반영되어 있다.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>app/domain/contracts.py, app/providers/narrative.py, app/config/default.yaml</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>대본 계약과 승인 체크포인트 정의 존재</t>
+        </is>
       </c>
       <c r="J7" s="2"/>
-      <c r="K7" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>556</v>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>파이프라인</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>골격구현</t>
+        </is>
       </c>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>634</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>REQ-VOICE-001</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>음성 단계는 NarrationContract와 자막 산출물을 사용</t>
+        </is>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>637</v>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>F-MEDIA-001</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>SCR-005</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>NarrationContract, TTS/STT provider 인터페이스, voice stage 파일이 현재 프로젝트에 존재한다.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>app/domain/contracts.py, app/providers/tts.py, app/providers/stt.py, app/stages/stage3_voice.py</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>나레이션 계약과 관련 provider/stage 골격이 존재</t>
+        </is>
       </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>556</v>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>파이프라인</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>골격구현</t>
+        </is>
       </c>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>638</v>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>REQ-VISUAL-001</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>스토리보드/에셋/렌더 단계는 계약 기반 체인을 사용</t>
+        </is>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>641</v>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>F-MEDIA-001</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SCR-006</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>StoryboardContract, AssetManifestContract, RenderPlanContract가 정의되어 있고 Stage 6에는 FFmpeg 기반 draft 렌더 코드가 존재한다.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>app/domain/contracts.py, app/providers/asset.py, app/services/ffmpeg_service.py, app/services/pillow_service.py, app/stages/stage4_storyboard.py ~ stage6_render.py</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Stage 4~5 관련 파일 존재, Stage 6은 draft.mp4 / render_plan.json 생성 로직 존재</t>
+        </is>
       </c>
       <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>556</v>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>파이프라인</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>일부구현</t>
+        </is>
       </c>
       <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>643</v>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>REQ-COST-001</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>비용 통제 설정과 검사 로직 존재</t>
+        </is>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>647</v>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>F-EXEC-001, F-GOV-001</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>SCR-002</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>default.yaml에는 stage별 hard cap과 provider limit가 정의되어 있고 CostGuardrail 클래스가 이를 읽는다.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>app/config/default.yaml, app/core/cost_guardrail.py</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>cost_guardrail 설정과 검사 코드 존재</t>
+        </is>
       </c>
       <c r="J10" s="2"/>
-      <c r="K10" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>534</v>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>파이프라인</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>일부구현</t>
+        </is>
       </c>
       <c r="M10" s="2"/>
     </row>
@@ -6367,61 +6909,89 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>496</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>MS-01</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Stage 0 ~ Stage 6(draft.mp4 생성)까지 구현</t>
+        </is>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>649</v>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>설계서 15장 Phase 1 범위</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>F-PROJ-001, F-EXEC-001, F-BENCH-001, F-SCRIPT-001, F-MEDIA-001</t>
+        </is>
       </c>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>651</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MS-02</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>썸네일, YouTube 업로드, Sora 비디오 생성, 비용 리포트 UI, final.mp4</t>
+        </is>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
-        <v>500</v>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>설계서 15장 Phase 2 범위</t>
+        </is>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>653</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>MS-03</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>웹 UI, 다중 채널 프리셋, 템플릿 반복 제작, A/B 썸네일, BGM</t>
+        </is>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
-        <v>654</v>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>설계서 15장 Phase 3 범위</t>
+        </is>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -6529,99 +7099,147 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>657</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RISK-001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>현재 코드</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>pydantic-settings 의존성 누락</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>app/settings.py는 pydantic_settings.BaseSettings를 import하지만 pyproject.toml 기본 의존성에는 pydantic-settings가 없다.</t>
+        </is>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
-        <v>658</v>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="2" t="s">
-        <v>659</v>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>app/settings.py, pyproject.toml</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>661</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RISK-002</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>현재 코드</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>DB init 중복 호출</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>AppContainer.init()와 PipelineOrchestrator.initialize()가 모두 self.db.init()를 호출한다.</t>
+        </is>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="2" t="s">
-        <v>658</v>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="2" t="s">
-        <v>662</v>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>app/main.py, app/core/orchestrator.py</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>664</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>RISK-003</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>현재 코드</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Artifact 저장/조회 형식 불일치</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Artifact 모델의 list/dict 필드와 SQLite 저장/조회 형식이 직접 대응하지 않아 조회 시 불일치 가능성이 있다.</t>
+        </is>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2" t="s">
-        <v>658</v>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="2" t="s">
-        <v>665</v>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>app/domain/models.py, app/storage/sqlite.py, app/core/artifact_registry.py</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>667</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RISK-004</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>현재 코드</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>fake provider 일부의 /tmp 경로 사용</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>FFmpegService는 tempfile로 전환되었으나 fake provider 일부는 여전히 /tmp 경로를 사용한다.</t>
+        </is>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2" t="s">
-        <v>658</v>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="2" t="s">
-        <v>668</v>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>app/services/ffmpeg_service.py, app/providers/fake.py</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6697,171 +7315,267 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>672</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TC-001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROJ-001</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>SCR-001</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>프로젝트 생성 후 slug와 상태 저장 확인</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>유효한 topic 입력, DB 경로 접근 가능</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>yt project create --topic '테스트 주제'</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>project가 생성되고 slug, status, created_at이 저장된다.</t>
+        </is>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="2" t="s">
-        <v>673</v>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>설계서 검증 방법 1번 기반</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>677</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC-002</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>REQ-EXEC-001</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SCR-002</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>동일 execution_digest에서 실행 모드 결정 확인</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>이전 stage run 이력 존재</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>skip / resume / overwrite 조합으로 stage executor 호출</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>mode와 이전 상태에 따라 skip, resume, execute 결정이 달라진다.</t>
+        </is>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="2" t="s">
-        <v>678</v>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>설계서 검증 방법 6,7번 기반</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>682</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TC-003</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>REQ-GOV-001</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>SCR-004</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>approval 상태 전이 확인</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>approval_id 존재</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>yt approve &lt;approval_id&gt; 또는 yt reject &lt;approval_id&gt;</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>approval 상태가 APPROVED 또는 REJECTED로 저장된다.</t>
+        </is>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="2" t="s">
-        <v>683</v>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>설계서 검증 방법 3번 기반</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>687</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC-004</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>REQ-BENCH-001</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>SCR-003</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>BenchmarkReport 계약 생성 확인</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>benchmark stage 실행 가능 상태</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>yt stage run &lt;slug&gt; benchmark</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>BenchmarkReport contract 파일과 quality gate 검증 대상이 생성된다.</t>
+        </is>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="2" t="s">
-        <v>688</v>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>설계서 검증 방법 2번 기반</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>692</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC-005</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>REQ-VOICE-001</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>SCR-005</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>NarrationContract와 자막 산출물 생성 확인</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>voice stage 실행 가능 상태</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>voice stage 실행</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>narration.wav, subtitles.srt, NarrationContract가 생성된다.</t>
+        </is>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="2" t="s">
-        <v>693</v>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>설계서 7장 stage 설명 기반</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>697</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC-006</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>REQ-VISUAL-001</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SCR-006</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>RenderStage 입력 계약 기반 draft 산출 확인</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>NarrationContract, StoryboardContract, AssetManifestContract와 출력 경로가 준비됨</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>RenderStage execute 호출</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>06_render에 render_plan.json과 draft.mp4가 생성되고 RenderPlanContract가 반환된다.</t>
+        </is>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="2" t="s">
-        <v>698</v>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>app/stages/stage6_render.py 현재 코드 기준</t>
+        </is>
       </c>
     </row>
   </sheetData>
